--- a/artfynd/A 48935-2020 artfynd.xlsx
+++ b/artfynd/A 48935-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48935-2020 artfynd.xlsx
+++ b/artfynd/A 48935-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,6 +1980,142 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120599543</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56214</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vakåsvägen, Nerigården, Hudiksvalls kommun, Gävleborgs län, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568085</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6892795</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Boxmodell: Wildlife Acoustics SM4/SMminiBat, Samplerate: 384khz</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Ambjorn Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
